--- a/北部山头3940平台2026/7、单日数据/北部山头3940平台-1008/二次圈矿成果_3940_1008_auto/3940平台 1008炮孔数据报告.xlsx
+++ b/北部山头3940平台2026/7、单日数据/北部山头3940平台-1008/二次圈矿成果_3940_1008_auto/3940平台 1008炮孔数据报告.xlsx
@@ -521,16 +521,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1843.904</v>
+        <v>1922.693</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>4978.54</v>
+        <v>5191.271</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>1.204</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>59.959</v>
+        <v>62.521</v>
       </c>
     </row>
     <row r="4">
@@ -541,16 +541,16 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n">
-        <v>1843.904</v>
+        <v>1922.693</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>4978.54</v>
+        <v>5191.271</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>1.204</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>59.959</v>
+        <v>62.521</v>
       </c>
     </row>
     <row r="5">
@@ -563,16 +563,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1376.882</v>
+        <v>1298.658</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3717.581</v>
+        <v>3506.375</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.729</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>27.106</v>
+        <v>25.566</v>
       </c>
     </row>
     <row r="6">
@@ -585,16 +585,16 @@
         <v>3</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>653.518</v>
+        <v>653.039</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1764.5</v>
+        <v>1763.206</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.68</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>11.999</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="7">
@@ -605,16 +605,16 @@
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="7" t="n">
-        <v>2030.4</v>
+        <v>1951.697</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>5482.081</v>
+        <v>5269.581</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0.713</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>39.105</v>
+        <v>37.556</v>
       </c>
     </row>
     <row r="8">
@@ -625,16 +625,16 @@
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="n">
-        <v>3874.304</v>
+        <v>3874.39</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>10460.621</v>
+        <v>10460.852</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.947</v>
+        <v>0.957</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>99.06399999999999</v>
+        <v>100.077</v>
       </c>
     </row>
     <row r="9">

--- a/北部山头3940平台2026/7、单日数据/北部山头3940平台-1008/二次圈矿成果_3940_1008_auto/3940平台 1008炮孔数据报告.xlsx
+++ b/北部山头3940平台2026/7、单日数据/北部山头3940平台-1008/二次圈矿成果_3940_1008_auto/3940平台 1008炮孔数据报告.xlsx
@@ -521,16 +521,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1922.693</v>
+        <v>1897.084</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>5191.271</v>
+        <v>5122.126</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>1.204</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>62.521</v>
+        <v>61.688</v>
       </c>
     </row>
     <row r="4">
@@ -541,16 +541,16 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n">
-        <v>1922.693</v>
+        <v>1897.084</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>5191.271</v>
+        <v>5122.126</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>1.204</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>62.521</v>
+        <v>61.688</v>
       </c>
     </row>
     <row r="5">
@@ -563,16 +563,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1298.658</v>
+        <v>1322.7</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3506.375</v>
+        <v>3571.291</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.729</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>25.566</v>
+        <v>26.039</v>
       </c>
     </row>
     <row r="6">
@@ -605,16 +605,16 @@
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="7" t="n">
-        <v>1951.697</v>
+        <v>1975.74</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>5269.581</v>
+        <v>5334.497</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0.713</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>37.556</v>
+        <v>38.029</v>
       </c>
     </row>
     <row r="8">
@@ -625,16 +625,16 @@
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="n">
-        <v>3874.39</v>
+        <v>3872.823</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>10460.852</v>
+        <v>10456.623</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.957</v>
+        <v>0.954</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>100.077</v>
+        <v>99.717</v>
       </c>
     </row>
     <row r="9">
